--- a/docentes/Desc Desc Desc - Estadisticos 20222.xlsx
+++ b/docentes/Desc Desc Desc - Estadisticos 20222.xlsx
@@ -3523,10 +3523,10 @@
         <v>55</v>
       </c>
       <c r="C76">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -3535,7 +3535,7 @@
         <v>24</v>
       </c>
       <c r="G76">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H76">
         <v>7.3</v>
@@ -3549,10 +3549,10 @@
         <v>56</v>
       </c>
       <c r="C77">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -3561,7 +3561,7 @@
         <v>28</v>
       </c>
       <c r="G77">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H77">
         <v>6.1</v>
@@ -6044,10 +6044,10 @@
         <v>55</v>
       </c>
       <c r="C76">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E76">
         <v>27</v>
@@ -6067,10 +6067,10 @@
         <v>56</v>
       </c>
       <c r="C77">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D77">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E77">
         <v>29</v>
@@ -8697,10 +8697,10 @@
         <v>55</v>
       </c>
       <c r="C76">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>11</v>
@@ -8709,7 +8709,7 @@
         <v>24</v>
       </c>
       <c r="G76">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H76">
         <v>6.8</v>
@@ -8723,10 +8723,10 @@
         <v>56</v>
       </c>
       <c r="C77">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -8735,7 +8735,7 @@
         <v>28</v>
       </c>
       <c r="G77">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H77">
         <v>6.1</v>
